--- a/output/coword/coword_termos_por_periodo.xlsx
+++ b/output/coword/coword_termos_por_periodo.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -456,11 +456,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>learning</t>
+          <t>networks</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -486,11 +486,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>intelligent</t>
+          <t>learning</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -501,11 +501,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>networks</t>
+          <t>intelligent</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -516,11 +516,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>brasileiro</t>
+          <t>universal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -531,11 +531,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>cham</t>
+          <t>brasileiro</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -546,11 +546,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>universal</t>
+          <t>dependencies</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -561,7 +561,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dependencies</t>
+          <t>universal dependencies</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -576,7 +576,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>universal dependencies</t>
+          <t>português</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -591,11 +591,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>português</t>
+          <t>artificial</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -606,7 +606,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>artificial</t>
+          <t>heterogeneous</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -621,7 +621,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>symposium</t>
+          <t>cham</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -636,11 +636,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>heterogeneous</t>
+          <t>estudo</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -651,7 +651,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>corpus</t>
+          <t>propagation</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -666,7 +666,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>informação</t>
+          <t>detection</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -711,7 +711,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>corpus</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -756,11 +756,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>propagation</t>
+          <t>agricultural</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -771,11 +771,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>areas</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -786,11 +786,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>estudo</t>
+          <t>scenarios</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -801,11 +801,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>automatic</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -816,11 +816,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>estimation</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -831,11 +831,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>information</t>
+          <t>sugarcane</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -846,7 +846,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>representation</t>
+          <t>unsupervised</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>science</t>
+          <t>unsupervised learning</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -876,7 +876,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>brasileiro tecnologia</t>
+          <t>biodiversidade</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>humana</t>
+          <t>biodiversidade estudo</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>informação linguagem</t>
+          <t>caso</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -921,7 +921,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>linguagem</t>
+          <t>contexto</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -936,7 +936,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>linguagem humana</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>segundo</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>tecnologia</t>
+          <t>estudo caso</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -981,7 +981,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>tecnologia informação</t>
+          <t>metadados</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>citação</t>
+          <t>attention</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>tagging</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>português brasileiro</t>
+          <t>representation</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>networks</t>
+          <t>learning</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46">
@@ -1101,11 +1101,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>artificial</t>
+          <t>dependencies</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47">
@@ -1116,11 +1116,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>learning</t>
+          <t>networks</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48">
@@ -1131,11 +1131,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>dependencies</t>
+          <t>universal</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49">
@@ -1146,11 +1146,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>universal</t>
+          <t>artificial</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50">
@@ -1176,11 +1176,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>neural</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52">
@@ -1191,11 +1191,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>neural</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>network</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1236,11 +1236,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>language</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56">
@@ -1251,11 +1251,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>speech</t>
+          <t>optimization</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57">
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>neural networks</t>
+          <t>speech</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59">
@@ -1296,11 +1296,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>recognition</t>
+          <t>modeling</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60">
@@ -1311,11 +1311,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>optimization</t>
+          <t>recognition</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61">
@@ -1326,11 +1326,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>modeling</t>
+          <t>evaluation</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>brazilian portuguese</t>
+          <t>neural networks</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>brazilian portuguese</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>models</t>
+          <t>deep</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>prediction</t>
+          <t>models</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>indigenous</t>
+          <t>prediction</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>deep</t>
+          <t>indigenous</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1461,11 +1461,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>september</t>
+          <t>social</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>corpus</t>
+          <t>detection</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>deep learning</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>climate</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>corpus</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>social</t>
+          <t>inteligência</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>natural</t>
+          <t>inteligência artificial</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>indigenous languages</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1596,11 +1596,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>indigenous languages</t>
+          <t>climate</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
@@ -1611,11 +1611,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>deep learning</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>resources</t>
+          <t>machine learning</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>portuguese</t>
+          <t>data</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>languages</t>
+          <t>portuguese</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>languages</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>brazilian portuguese</t>
+          <t>networks</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>artificial</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>processing</t>
+          <t>neural</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>neural</t>
+          <t>processing</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1821,11 +1821,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>artificial</t>
+          <t>brazilian portuguese</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
@@ -1836,11 +1836,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>networks</t>
+          <t>language</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">
@@ -1851,11 +1851,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>universal</t>
+          <t>intelligence</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>corpora</t>
+          <t>artificial intelligence</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>american</t>
+          <t>evaluation</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>universal</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>intelligence</t>
+          <t>corpora</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>appear</t>
+          <t>assessment</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>dependencies</t>
+          <t>latin</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>universal dependencies</t>
+          <t>neural networks</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>automatic</t>
+          <t>detection</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>metrics</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>speech processing</t>
+          <t>intelligent</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>spoken</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>metrics</t>
+          <t>appear</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>latin</t>
+          <t>dependencies</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>universal dependencies</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>intelligent</t>
+          <t>automatic</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>translators</t>
+          <t>development</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>speech processing</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>artificial intelligence</t>
+          <t>spoken</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>american</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>neural networks</t>
+          <t>training</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>translators</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2181,11 +2181,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>abralin</t>
+          <t>human</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>abralin appear</t>
+          <t>agricultura</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>corpus dantestocks</t>
+          <t>agricultura digital</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>dantestocks</t>
+          <t>digital</t>
         </is>
       </c>
       <c r="C121" t="n">

--- a/output/coword/coword_termos_por_periodo.xlsx
+++ b/output/coword/coword_termos_por_periodo.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>portuguese</t>
+          <t>learning</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -486,11 +486,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>learning</t>
+          <t>portuguese</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
